--- a/data/monthly/【2025年7月】月次数値.xlsx
+++ b/data/monthly/【2025年7月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -116,9 +115,6 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Instagram投稿: おいしいクレープ屋さんがあなたの街に！！</t>
-  </si>
-  <si>
     <t>archived</t>
   </si>
   <si>
@@ -138,31 +134,91 @@
   </si>
   <si>
     <t>竹内歯科クリニック（審美ジルコニア）</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>通算</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【銀座トレーニングラボ】
+“脚が変わる”は、立ち方から始まる。...</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,36 +226,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,14 +544,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y17"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -598,7 +651,7 @@
         <v>223</v>
       </c>
       <c r="I2">
-        <v>1.067265</v>
+        <v>1.0672649999999999</v>
       </c>
       <c r="J2">
         <v>85.5</v>
@@ -619,7 +672,7 @@
         <v>238</v>
       </c>
       <c r="P2">
-        <v>718.487395</v>
+        <v>718.48739499999999</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -628,19 +681,19 @@
         <v>85.5</v>
       </c>
       <c r="T2">
-        <v>0.840336</v>
+        <v>0.84033599999999997</v>
       </c>
       <c r="U2">
         <v>2</v>
       </c>
       <c r="V2">
-        <v>0.840336</v>
+        <v>0.84033599999999997</v>
       </c>
       <c r="W2">
         <v>85.5</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -648,67 +701,67 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
       </c>
       <c r="H3">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="I3">
-        <v>1.049296</v>
+        <v>1.022222</v>
       </c>
       <c r="J3">
-        <v>25.6</v>
-      </c>
-      <c r="K3">
-        <v>160</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O3">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="P3">
-        <v>859.060403</v>
+        <v>826.08695699999998</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>25.6</v>
+        <v>38</v>
       </c>
       <c r="T3">
-        <v>3.355705</v>
+        <v>2.1739130000000002</v>
       </c>
       <c r="U3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>4.026846</v>
+        <v>2.1739130000000002</v>
       </c>
       <c r="W3">
-        <v>21.333333</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -716,67 +769,49 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4">
+      <c r="H4">
+        <v>39</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4">
-        <v>45</v>
-      </c>
-      <c r="I4">
-        <v>1.022222</v>
-      </c>
-      <c r="J4">
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>53</v>
+      </c>
+      <c r="N4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>38</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4">
         <v>39</v>
       </c>
-      <c r="O4">
-        <v>46</v>
-      </c>
       <c r="P4">
-        <v>826.086957</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>38</v>
-      </c>
-      <c r="T4">
-        <v>2.173913</v>
+        <v>1358.974359</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>2.173913</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -784,60 +819,861 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="H5">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5">
+        <v>59000</v>
+      </c>
+      <c r="L5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5">
+        <v>19</v>
+      </c>
+      <c r="N5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5">
+        <v>18</v>
+      </c>
+      <c r="P5">
+        <v>1055.555556</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>59000</v>
+      </c>
+      <c r="L6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>400</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>1169</v>
+      </c>
+      <c r="I7">
+        <v>2.7861419999999999</v>
+      </c>
+      <c r="J7">
+        <v>76.717948719999995</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>2992</v>
+      </c>
+      <c r="N7" t="s">
         <v>38</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="O7">
+        <v>3257</v>
+      </c>
+      <c r="P7">
+        <v>918.63678200000004</v>
+      </c>
+      <c r="Q7">
+        <v>39</v>
+      </c>
+      <c r="S7">
+        <v>76.717949000000004</v>
+      </c>
+      <c r="T7">
+        <v>1.1974210000000001</v>
+      </c>
+      <c r="U7">
+        <v>43</v>
+      </c>
+      <c r="V7">
+        <v>1.320233</v>
+      </c>
+      <c r="W7">
+        <v>69.581395000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>2526</v>
+      </c>
+      <c r="I8">
+        <v>1.182898</v>
+      </c>
+      <c r="J8">
+        <v>59.86538462</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>3113</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8">
+        <v>2988</v>
+      </c>
+      <c r="P8">
+        <v>1041.8340029999999</v>
+      </c>
+      <c r="Q8">
+        <v>52</v>
+      </c>
+      <c r="S8">
+        <v>59.865385000000003</v>
+      </c>
+      <c r="T8">
+        <v>1.7402949999999999</v>
+      </c>
+      <c r="U8">
+        <v>58</v>
+      </c>
+      <c r="V8">
+        <v>1.941098</v>
+      </c>
+      <c r="W8">
+        <v>53.672414000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9">
+        <v>2358</v>
+      </c>
+      <c r="I9">
+        <v>1.282867</v>
+      </c>
+      <c r="J9">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>3124</v>
+      </c>
+      <c r="N9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9">
+        <v>3025</v>
+      </c>
+      <c r="P9">
+        <v>1032.727273</v>
+      </c>
+      <c r="Q9">
+        <v>40</v>
+      </c>
+      <c r="S9">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="T9">
+        <v>1.322314</v>
+      </c>
+      <c r="U9">
+        <v>44</v>
+      </c>
+      <c r="V9">
+        <v>1.454545</v>
+      </c>
+      <c r="W9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5">
-        <v>39</v>
-      </c>
-      <c r="P5">
-        <v>1358.974359</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>172</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>2046</v>
+      </c>
+      <c r="I10">
+        <v>1.451613</v>
+      </c>
+      <c r="J10">
+        <v>16.639534879999999</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>2862</v>
+      </c>
+      <c r="N10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10">
+        <v>2970</v>
+      </c>
+      <c r="P10">
+        <v>963.63636399999996</v>
+      </c>
+      <c r="Q10">
+        <v>172</v>
+      </c>
+      <c r="S10">
+        <v>16.639534999999999</v>
+      </c>
+      <c r="T10">
+        <v>5.7912460000000001</v>
+      </c>
+      <c r="U10">
+        <v>193</v>
+      </c>
+      <c r="V10">
+        <v>6.4983170000000001</v>
+      </c>
+      <c r="W10">
+        <v>14.829015999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>1991</v>
+      </c>
+      <c r="I11">
+        <v>1.418885</v>
+      </c>
+      <c r="J11">
+        <v>47.666666669999998</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>3003</v>
+      </c>
+      <c r="N11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11">
+        <v>2825</v>
+      </c>
+      <c r="P11">
+        <v>1063.0088499999999</v>
+      </c>
+      <c r="Q11">
+        <v>63</v>
+      </c>
+      <c r="S11">
+        <v>47.666666999999997</v>
+      </c>
+      <c r="T11">
+        <v>2.230089</v>
+      </c>
+      <c r="U11">
+        <v>67</v>
+      </c>
+      <c r="V11">
+        <v>2.3716810000000002</v>
+      </c>
+      <c r="W11">
+        <v>44.820895999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>1370</v>
+      </c>
+      <c r="I12">
+        <v>1.520438</v>
+      </c>
+      <c r="J12">
+        <v>23.887323940000002</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1696</v>
+      </c>
+      <c r="N12" t="s">
+        <v>46</v>
+      </c>
+      <c r="O12">
+        <v>2083</v>
+      </c>
+      <c r="P12">
+        <v>814.21027400000003</v>
+      </c>
+      <c r="Q12">
+        <v>71</v>
+      </c>
+      <c r="S12">
+        <v>23.887324</v>
+      </c>
+      <c r="T12">
+        <v>3.4085450000000002</v>
+      </c>
+      <c r="U12">
+        <v>92</v>
+      </c>
+      <c r="V12">
+        <v>4.4167069999999997</v>
+      </c>
+      <c r="W12">
+        <v>18.434782999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>101</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>1505</v>
+      </c>
+      <c r="I13">
+        <v>1.4823919999999999</v>
+      </c>
+      <c r="J13">
+        <v>16.693069309999998</v>
+      </c>
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1686</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13">
+        <v>2231</v>
+      </c>
+      <c r="P13">
+        <v>755.71492599999999</v>
+      </c>
+      <c r="Q13">
+        <v>101</v>
+      </c>
+      <c r="S13">
+        <v>16.693069000000001</v>
+      </c>
+      <c r="T13">
+        <v>4.5271179999999998</v>
+      </c>
+      <c r="U13">
+        <v>129</v>
+      </c>
+      <c r="V13">
+        <v>5.7821600000000002</v>
+      </c>
+      <c r="W13">
+        <v>13.069767000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>1136</v>
+      </c>
+      <c r="I14">
+        <v>1.395246</v>
+      </c>
+      <c r="J14">
+        <v>29.403225809999999</v>
+      </c>
+      <c r="K14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1823</v>
+      </c>
+      <c r="N14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14">
+        <v>1585</v>
+      </c>
+      <c r="P14">
+        <v>1150.157729</v>
+      </c>
+      <c r="Q14">
+        <v>62</v>
+      </c>
+      <c r="S14">
+        <v>29.403226</v>
+      </c>
+      <c r="T14">
+        <v>3.9116719999999998</v>
+      </c>
+      <c r="U14">
+        <v>68</v>
+      </c>
+      <c r="V14">
+        <v>4.2902209999999998</v>
+      </c>
+      <c r="W14">
+        <v>26.808824000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>451</v>
+      </c>
+      <c r="I15">
+        <v>1.0820399999999999</v>
+      </c>
+      <c r="J15">
+        <v>34.705882350000003</v>
+      </c>
+      <c r="K15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>590</v>
+      </c>
+      <c r="N15" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15">
+        <v>488</v>
+      </c>
+      <c r="P15">
+        <v>1209.0163930000001</v>
+      </c>
+      <c r="Q15">
+        <v>17</v>
+      </c>
+      <c r="S15">
+        <v>34.705882000000003</v>
+      </c>
+      <c r="T15">
+        <v>3.4836070000000001</v>
+      </c>
+      <c r="U15">
+        <v>21</v>
+      </c>
+      <c r="V15">
+        <v>4.3032789999999999</v>
+      </c>
+      <c r="W15">
+        <v>28.095237999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>54</v>
+      </c>
+      <c r="I16">
+        <v>1.018519</v>
+      </c>
+      <c r="J16">
+        <v>90</v>
+      </c>
+      <c r="K16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>90</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16">
+        <v>55</v>
+      </c>
+      <c r="P16">
+        <v>1636.363636</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>90</v>
+      </c>
+      <c r="T16">
+        <v>1.818182</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1.818182</v>
+      </c>
+      <c r="W16">
+        <v>90</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>72</v>
+      </c>
+      <c r="I17">
+        <v>1.0277780000000001</v>
+      </c>
+      <c r="J17">
+        <v>63</v>
+      </c>
+      <c r="K17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>63</v>
+      </c>
+      <c r="N17" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17">
+        <v>74</v>
+      </c>
+      <c r="P17">
+        <v>851.35135100000002</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>63</v>
+      </c>
+      <c r="T17">
+        <v>1.351351</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1.351351</v>
+      </c>
+      <c r="W17">
+        <v>63</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>